--- a/test_data/Orion_Stress_Demo/PN-BETA-02/40202/BU02/HRM/post DFS_HRM-2031-0452/Panel 02/front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU02_Front_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-BETA-02/40202/BU02/HRM/post DFS_HRM-2031-0452/Panel 02/front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU02_Front_Summary.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J30"/>
+  <dimension ref="A1:J40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -460,22 +460,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>16.8363</v>
+        <v>16.77482</v>
       </c>
       <c r="D2" t="n">
-        <v>16.82681</v>
+        <v>16.53688</v>
       </c>
       <c r="E2" t="n">
-        <v>16.81774</v>
+        <v>16.62704</v>
       </c>
       <c r="F2" t="n">
-        <v>42.96904</v>
+        <v>42.75764</v>
       </c>
       <c r="G2" t="n">
-        <v>0.05091</v>
+        <v>0.05104</v>
       </c>
       <c r="H2" t="n">
-        <v>1.77898</v>
+        <v>1.81476</v>
       </c>
     </row>
     <row r="3">
@@ -485,22 +485,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>16.7845</v>
+        <v>16.6247</v>
       </c>
       <c r="D3" t="n">
-        <v>16.66876</v>
+        <v>16.47361</v>
       </c>
       <c r="E3" t="n">
-        <v>16.66163</v>
+        <v>16.47667</v>
       </c>
       <c r="F3" t="n">
-        <v>43.11236</v>
+        <v>42.45029</v>
       </c>
       <c r="G3" t="n">
-        <v>0.05136</v>
+        <v>0.05061</v>
       </c>
       <c r="H3" t="n">
-        <v>1.8042</v>
+        <v>1.82556</v>
       </c>
     </row>
     <row r="4">
@@ -510,22 +510,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>16.6463</v>
+        <v>16.92567</v>
       </c>
       <c r="D4" t="n">
-        <v>16.88395</v>
+        <v>16.43974</v>
       </c>
       <c r="E4" t="n">
-        <v>16.48423</v>
+        <v>16.53316</v>
       </c>
       <c r="F4" t="n">
-        <v>42.10196</v>
+        <v>41.55014</v>
       </c>
       <c r="G4" t="n">
-        <v>0.05028</v>
+        <v>0.05022</v>
       </c>
       <c r="H4" t="n">
-        <v>1.85679</v>
+        <v>1.81528</v>
       </c>
     </row>
     <row r="5">
@@ -535,22 +535,22 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>16.58881</v>
+        <v>16.79486</v>
       </c>
       <c r="D5" t="n">
-        <v>16.4325</v>
+        <v>16.391</v>
       </c>
       <c r="E5" t="n">
-        <v>16.77803</v>
+        <v>16.71318</v>
       </c>
       <c r="F5" t="n">
-        <v>41.68089</v>
+        <v>41.73505</v>
       </c>
       <c r="G5" t="n">
-        <v>0.05101</v>
+        <v>0.04978</v>
       </c>
       <c r="H5" t="n">
-        <v>1.81444</v>
+        <v>1.83287</v>
       </c>
     </row>
     <row r="6">
@@ -560,22 +560,22 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>16.97866</v>
+        <v>16.7314</v>
       </c>
       <c r="D6" t="n">
-        <v>16.80541</v>
+        <v>16.68276</v>
       </c>
       <c r="E6" t="n">
-        <v>16.8821</v>
+        <v>16.71063</v>
       </c>
       <c r="F6" t="n">
-        <v>42.14893</v>
+        <v>42.70748</v>
       </c>
       <c r="G6" t="n">
-        <v>0.05154</v>
+        <v>0.05121</v>
       </c>
       <c r="H6" t="n">
-        <v>1.82732</v>
+        <v>1.82541</v>
       </c>
     </row>
     <row r="7">
@@ -585,22 +585,22 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>16.94335</v>
+        <v>16.54562</v>
       </c>
       <c r="D7" t="n">
-        <v>16.55452</v>
+        <v>16.25662</v>
       </c>
       <c r="E7" t="n">
-        <v>16.64846</v>
+        <v>16.33007</v>
       </c>
       <c r="F7" t="n">
-        <v>42.95711</v>
+        <v>42.8556</v>
       </c>
       <c r="G7" t="n">
-        <v>0.05111</v>
+        <v>0.05122</v>
       </c>
       <c r="H7" t="n">
-        <v>1.84</v>
+        <v>1.82599</v>
       </c>
     </row>
     <row r="8">
@@ -610,22 +610,22 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>16.31986</v>
+        <v>16.789</v>
       </c>
       <c r="D8" t="n">
-        <v>16.38108</v>
+        <v>16.37362</v>
       </c>
       <c r="E8" t="n">
-        <v>16.47846</v>
+        <v>16.53491</v>
       </c>
       <c r="F8" t="n">
-        <v>43.43077</v>
+        <v>42.31983</v>
       </c>
       <c r="G8" t="n">
-        <v>0.05139</v>
+        <v>0.05038</v>
       </c>
       <c r="H8" t="n">
-        <v>1.81536</v>
+        <v>1.82122</v>
       </c>
     </row>
     <row r="9">
@@ -635,22 +635,22 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>16.65158</v>
+        <v>16.80298</v>
       </c>
       <c r="D9" t="n">
-        <v>16.44668</v>
+        <v>16.6357</v>
       </c>
       <c r="E9" t="n">
-        <v>16.86641</v>
+        <v>16.64948</v>
       </c>
       <c r="F9" t="n">
-        <v>43.33456</v>
+        <v>42.78782</v>
       </c>
       <c r="G9" t="n">
-        <v>0.04999</v>
+        <v>0.05017</v>
       </c>
       <c r="H9" t="n">
-        <v>1.80363</v>
+        <v>1.81679</v>
       </c>
     </row>
     <row r="10">
@@ -660,22 +660,22 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>16.40545</v>
+        <v>16.75772</v>
       </c>
       <c r="D10" t="n">
-        <v>16.73824</v>
+        <v>16.5158</v>
       </c>
       <c r="E10" t="n">
-        <v>16.96722</v>
+        <v>16.66612</v>
       </c>
       <c r="F10" t="n">
-        <v>42.91378</v>
+        <v>42.67388</v>
       </c>
       <c r="G10" t="n">
-        <v>0.05034</v>
+        <v>0.05067</v>
       </c>
       <c r="H10" t="n">
-        <v>1.82513</v>
+        <v>1.85294</v>
       </c>
     </row>
     <row r="11">
@@ -696,12 +696,17 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Width</t>
+          <t>Radius</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Space</t>
+          <t>Dimple</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Bump</t>
         </is>
       </c>
     </row>
@@ -713,8 +718,26 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Trace 1</t>
-        </is>
+          <t>Pad 1</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>16.98711</v>
+      </c>
+      <c r="D12" t="n">
+        <v>16.47524</v>
+      </c>
+      <c r="E12" t="n">
+        <v>16.66864</v>
+      </c>
+      <c r="F12" t="n">
+        <v>42.14036</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.05143</v>
+      </c>
+      <c r="H12" t="n">
+        <v>1.81585</v>
       </c>
     </row>
     <row r="13">
@@ -723,6 +746,24 @@
           <t>Unit 8</t>
         </is>
       </c>
+      <c r="C13" t="n">
+        <v>16.79282</v>
+      </c>
+      <c r="D13" t="n">
+        <v>16.26683</v>
+      </c>
+      <c r="E13" t="n">
+        <v>16.53223</v>
+      </c>
+      <c r="F13" t="n">
+        <v>42.69262</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.0504</v>
+      </c>
+      <c r="H13" t="n">
+        <v>1.82213</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -730,6 +771,24 @@
           <t>Unit 9</t>
         </is>
       </c>
+      <c r="C14" t="n">
+        <v>17.00733</v>
+      </c>
+      <c r="D14" t="n">
+        <v>16.51953</v>
+      </c>
+      <c r="E14" t="n">
+        <v>16.94251</v>
+      </c>
+      <c r="F14" t="n">
+        <v>42.10591</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.05199</v>
+      </c>
+      <c r="H14" t="n">
+        <v>1.7802</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -737,6 +796,24 @@
           <t>Unit 4</t>
         </is>
       </c>
+      <c r="C15" t="n">
+        <v>16.89388</v>
+      </c>
+      <c r="D15" t="n">
+        <v>16.6611</v>
+      </c>
+      <c r="E15" t="n">
+        <v>16.73694</v>
+      </c>
+      <c r="F15" t="n">
+        <v>42.79757</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.051</v>
+      </c>
+      <c r="H15" t="n">
+        <v>1.81498</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -744,6 +821,24 @@
           <t>Unit 5</t>
         </is>
       </c>
+      <c r="C16" t="n">
+        <v>16.82552</v>
+      </c>
+      <c r="D16" t="n">
+        <v>16.61736</v>
+      </c>
+      <c r="E16" t="n">
+        <v>16.73868</v>
+      </c>
+      <c r="F16" t="n">
+        <v>43.14947</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.05133</v>
+      </c>
+      <c r="H16" t="n">
+        <v>1.79411</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -751,6 +846,24 @@
           <t>Unit 6</t>
         </is>
       </c>
+      <c r="C17" t="n">
+        <v>16.74788</v>
+      </c>
+      <c r="D17" t="n">
+        <v>16.47019</v>
+      </c>
+      <c r="E17" t="n">
+        <v>16.59654</v>
+      </c>
+      <c r="F17" t="n">
+        <v>42.36027</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0.05085</v>
+      </c>
+      <c r="H17" t="n">
+        <v>1.884</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -758,6 +871,24 @@
           <t>Unit 1</t>
         </is>
       </c>
+      <c r="C18" t="n">
+        <v>16.63634</v>
+      </c>
+      <c r="D18" t="n">
+        <v>16.44837</v>
+      </c>
+      <c r="E18" t="n">
+        <v>16.4659</v>
+      </c>
+      <c r="F18" t="n">
+        <v>42.79995</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0.05166</v>
+      </c>
+      <c r="H18" t="n">
+        <v>1.83648</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -765,6 +896,24 @@
           <t>Unit 2</t>
         </is>
       </c>
+      <c r="C19" t="n">
+        <v>16.80125</v>
+      </c>
+      <c r="D19" t="n">
+        <v>16.45327</v>
+      </c>
+      <c r="E19" t="n">
+        <v>16.79678</v>
+      </c>
+      <c r="F19" t="n">
+        <v>41.51603</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0.05069</v>
+      </c>
+      <c r="H19" t="n">
+        <v>1.82732</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -772,46 +921,34 @@
           <t>Unit 3</t>
         </is>
       </c>
+      <c r="C20" t="n">
+        <v>16.92024</v>
+      </c>
+      <c r="D20" t="n">
+        <v>16.62148</v>
+      </c>
+      <c r="E20" t="n">
+        <v>16.89732</v>
+      </c>
+      <c r="F20" t="n">
+        <v>42.94053</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0.05057</v>
+      </c>
+      <c r="H20" t="n">
+        <v>1.81537</v>
+      </c>
     </row>
     <row r="21">
       <c r="C21" t="inlineStr">
         <is>
-          <t>Rz max</t>
+          <t>Dimple</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Rz mean</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>Rz min</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>Rz max</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>Ra mean</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>Ra Std dev</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>Ra min</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>Ra max</t>
+          <t>Bump</t>
         </is>
       </c>
     </row>
@@ -823,32 +960,14 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>roughness</t>
+          <t>via 1</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.74388</v>
+        <v>0.606</v>
       </c>
       <c r="D22" t="n">
-        <v>0.08093</v>
-      </c>
-      <c r="E22" t="n">
-        <v>0.61099</v>
-      </c>
-      <c r="F22" t="n">
-        <v>0.9599</v>
-      </c>
-      <c r="G22" t="n">
-        <v>0.11103</v>
-      </c>
-      <c r="H22" t="n">
-        <v>0.00756</v>
-      </c>
-      <c r="I22" t="n">
-        <v>0.09295</v>
-      </c>
-      <c r="J22" t="n">
-        <v>0.12562</v>
+        <v>1.11885</v>
       </c>
     </row>
     <row r="23">
@@ -858,28 +977,10 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.73634</v>
+        <v>0.60464</v>
       </c>
       <c r="D23" t="n">
-        <v>0.07964</v>
-      </c>
-      <c r="E23" t="n">
-        <v>0.61124</v>
-      </c>
-      <c r="F23" t="n">
-        <v>0.9352</v>
-      </c>
-      <c r="G23" t="n">
-        <v>0.10872</v>
-      </c>
-      <c r="H23" t="n">
-        <v>0.00754</v>
-      </c>
-      <c r="I23" t="n">
-        <v>0.09464</v>
-      </c>
-      <c r="J23" t="n">
-        <v>0.1239</v>
+        <v>1.1136</v>
       </c>
     </row>
     <row r="24">
@@ -889,28 +990,10 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.74662</v>
+        <v>0.61282</v>
       </c>
       <c r="D24" t="n">
-        <v>0.08261</v>
-      </c>
-      <c r="E24" t="n">
-        <v>0.62143</v>
-      </c>
-      <c r="F24" t="n">
-        <v>0.95357</v>
-      </c>
-      <c r="G24" t="n">
-        <v>0.1072</v>
-      </c>
-      <c r="H24" t="n">
-        <v>0.00752</v>
-      </c>
-      <c r="I24" t="n">
-        <v>0.09297999999999999</v>
-      </c>
-      <c r="J24" t="n">
-        <v>0.12364</v>
+        <v>1.11071</v>
       </c>
     </row>
     <row r="25">
@@ -920,28 +1003,10 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0.75596</v>
+        <v>0.60976</v>
       </c>
       <c r="D25" t="n">
-        <v>0.08103</v>
-      </c>
-      <c r="E25" t="n">
-        <v>0.61287</v>
-      </c>
-      <c r="F25" t="n">
-        <v>0.95101</v>
-      </c>
-      <c r="G25" t="n">
-        <v>0.10893</v>
-      </c>
-      <c r="H25" t="n">
-        <v>0.00763</v>
-      </c>
-      <c r="I25" t="n">
-        <v>0.09356</v>
-      </c>
-      <c r="J25" t="n">
-        <v>0.12606</v>
+        <v>1.13115</v>
       </c>
     </row>
     <row r="26">
@@ -951,28 +1016,10 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.7500599999999999</v>
+        <v>0.6190600000000001</v>
       </c>
       <c r="D26" t="n">
-        <v>0.08055</v>
-      </c>
-      <c r="E26" t="n">
-        <v>0.62034</v>
-      </c>
-      <c r="F26" t="n">
-        <v>0.95333</v>
-      </c>
-      <c r="G26" t="n">
-        <v>0.11234</v>
-      </c>
-      <c r="H26" t="n">
-        <v>0.00775</v>
-      </c>
-      <c r="I26" t="n">
-        <v>0.09447</v>
-      </c>
-      <c r="J26" t="n">
-        <v>0.1282</v>
+        <v>1.11844</v>
       </c>
     </row>
     <row r="27">
@@ -982,28 +1029,10 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0.7498899999999999</v>
+        <v>0.61343</v>
       </c>
       <c r="D27" t="n">
-        <v>0.08137</v>
-      </c>
-      <c r="E27" t="n">
-        <v>0.60487</v>
-      </c>
-      <c r="F27" t="n">
-        <v>0.9688600000000001</v>
-      </c>
-      <c r="G27" t="n">
-        <v>0.10756</v>
-      </c>
-      <c r="H27" t="n">
-        <v>0.00765</v>
-      </c>
-      <c r="I27" t="n">
-        <v>0.09420000000000001</v>
-      </c>
-      <c r="J27" t="n">
-        <v>0.12574</v>
+        <v>1.11937</v>
       </c>
     </row>
     <row r="28">
@@ -1013,28 +1042,10 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0.74712</v>
+        <v>0.60126</v>
       </c>
       <c r="D28" t="n">
-        <v>0.08075</v>
-      </c>
-      <c r="E28" t="n">
-        <v>0.6123</v>
-      </c>
-      <c r="F28" t="n">
-        <v>0.9763500000000001</v>
-      </c>
-      <c r="G28" t="n">
-        <v>0.10909</v>
-      </c>
-      <c r="H28" t="n">
-        <v>0.00772</v>
-      </c>
-      <c r="I28" t="n">
-        <v>0.09272</v>
-      </c>
-      <c r="J28" t="n">
-        <v>0.12564</v>
+        <v>1.12799</v>
       </c>
     </row>
     <row r="29">
@@ -1044,28 +1055,10 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0.74134</v>
+        <v>0.59605</v>
       </c>
       <c r="D29" t="n">
-        <v>0.08155999999999999</v>
-      </c>
-      <c r="E29" t="n">
-        <v>0.60695</v>
-      </c>
-      <c r="F29" t="n">
-        <v>0.96399</v>
-      </c>
-      <c r="G29" t="n">
-        <v>0.10965</v>
-      </c>
-      <c r="H29" t="n">
-        <v>0.00763</v>
-      </c>
-      <c r="I29" t="n">
-        <v>0.09525</v>
-      </c>
-      <c r="J29" t="n">
-        <v>0.12622</v>
+        <v>1.11241</v>
       </c>
     </row>
     <row r="30">
@@ -1075,28 +1068,336 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>0.75967</v>
+        <v>0.60059</v>
       </c>
       <c r="D30" t="n">
-        <v>0.07969</v>
-      </c>
-      <c r="E30" t="n">
-        <v>0.6081800000000001</v>
-      </c>
-      <c r="F30" t="n">
-        <v>0.97011</v>
-      </c>
-      <c r="G30" t="n">
-        <v>0.10843</v>
-      </c>
-      <c r="H30" t="n">
-        <v>0.00759</v>
-      </c>
-      <c r="I30" t="n">
-        <v>0.09465</v>
-      </c>
-      <c r="J30" t="n">
-        <v>0.12602</v>
+        <v>1.11035</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Rz max</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Rz mean</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Rz min</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Rz max</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Ra mean</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Ra Std dev</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>Ra min</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>Ra max</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Unit 7</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>roughness</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>0.74735</v>
+      </c>
+      <c r="D32" t="n">
+        <v>0.08024000000000001</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0.62444</v>
+      </c>
+      <c r="F32" t="n">
+        <v>0.94867</v>
+      </c>
+      <c r="G32" t="n">
+        <v>0.11104</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0.00745</v>
+      </c>
+      <c r="I32" t="n">
+        <v>0.09331</v>
+      </c>
+      <c r="J32" t="n">
+        <v>0.12891</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Unit 8</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>0.74391</v>
+      </c>
+      <c r="D33" t="n">
+        <v>0.08149000000000001</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0.60701</v>
+      </c>
+      <c r="F33" t="n">
+        <v>0.98705</v>
+      </c>
+      <c r="G33" t="n">
+        <v>0.1113</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0.00764</v>
+      </c>
+      <c r="I33" t="n">
+        <v>0.09276</v>
+      </c>
+      <c r="J33" t="n">
+        <v>0.12577</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Unit 9</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>0.7537700000000001</v>
+      </c>
+      <c r="D34" t="n">
+        <v>0.08109</v>
+      </c>
+      <c r="E34" t="n">
+        <v>0.59977</v>
+      </c>
+      <c r="F34" t="n">
+        <v>0.97622</v>
+      </c>
+      <c r="G34" t="n">
+        <v>0.10831</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0.00765</v>
+      </c>
+      <c r="I34" t="n">
+        <v>0.09306</v>
+      </c>
+      <c r="J34" t="n">
+        <v>0.1293</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Unit 4</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>0.77177</v>
+      </c>
+      <c r="D35" t="n">
+        <v>0.07943</v>
+      </c>
+      <c r="E35" t="n">
+        <v>0.60048</v>
+      </c>
+      <c r="F35" t="n">
+        <v>0.97504</v>
+      </c>
+      <c r="G35" t="n">
+        <v>0.10912</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0.00768</v>
+      </c>
+      <c r="I35" t="n">
+        <v>0.09311</v>
+      </c>
+      <c r="J35" t="n">
+        <v>0.1267</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Unit 5</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>0.74991</v>
+      </c>
+      <c r="D36" t="n">
+        <v>0.08198</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0.60676</v>
+      </c>
+      <c r="F36" t="n">
+        <v>0.9594</v>
+      </c>
+      <c r="G36" t="n">
+        <v>0.10989</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0.00756</v>
+      </c>
+      <c r="I36" t="n">
+        <v>0.09490999999999999</v>
+      </c>
+      <c r="J36" t="n">
+        <v>0.12761</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Unit 6</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>0.76308</v>
+      </c>
+      <c r="D37" t="n">
+        <v>0.08098</v>
+      </c>
+      <c r="E37" t="n">
+        <v>0.60337</v>
+      </c>
+      <c r="F37" t="n">
+        <v>0.97831</v>
+      </c>
+      <c r="G37" t="n">
+        <v>0.10727</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0.00754</v>
+      </c>
+      <c r="I37" t="n">
+        <v>0.09429</v>
+      </c>
+      <c r="J37" t="n">
+        <v>0.12533</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Unit 1</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>0.75586</v>
+      </c>
+      <c r="D38" t="n">
+        <v>0.08123</v>
+      </c>
+      <c r="E38" t="n">
+        <v>0.61526</v>
+      </c>
+      <c r="F38" t="n">
+        <v>0.9511500000000001</v>
+      </c>
+      <c r="G38" t="n">
+        <v>0.10679</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0.0077</v>
+      </c>
+      <c r="I38" t="n">
+        <v>0.09439</v>
+      </c>
+      <c r="J38" t="n">
+        <v>0.12525</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Unit 2</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>0.7521</v>
+      </c>
+      <c r="D39" t="n">
+        <v>0.08180999999999999</v>
+      </c>
+      <c r="E39" t="n">
+        <v>0.60095</v>
+      </c>
+      <c r="F39" t="n">
+        <v>0.98008</v>
+      </c>
+      <c r="G39" t="n">
+        <v>0.10932</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0.00766</v>
+      </c>
+      <c r="I39" t="n">
+        <v>0.09426</v>
+      </c>
+      <c r="J39" t="n">
+        <v>0.12716</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Unit 3</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>0.74122</v>
+      </c>
+      <c r="D40" t="n">
+        <v>0.07974000000000001</v>
+      </c>
+      <c r="E40" t="n">
+        <v>0.6028</v>
+      </c>
+      <c r="F40" t="n">
+        <v>0.98494</v>
+      </c>
+      <c r="G40" t="n">
+        <v>0.10986</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0.00757</v>
+      </c>
+      <c r="I40" t="n">
+        <v>0.09316000000000001</v>
+      </c>
+      <c r="J40" t="n">
+        <v>0.12711</v>
       </c>
     </row>
   </sheetData>
